--- a/artfynd/A 36098-2023 artfynd.xlsx
+++ b/artfynd/A 36098-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376200</v>
       </c>
       <c r="B2" t="n">
-        <v>61592</v>
+        <v>61596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376201</v>
       </c>
       <c r="B3" t="n">
-        <v>103995</v>
+        <v>104001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36098-2023 artfynd.xlsx
+++ b/artfynd/A 36098-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137376201</v>
       </c>
       <c r="B3" t="n">
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36098-2023 artfynd.xlsx
+++ b/artfynd/A 36098-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137376201</v>
       </c>
       <c r="B3" t="n">
-        <v>104002</v>
+        <v>104014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36098-2023 artfynd.xlsx
+++ b/artfynd/A 36098-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137376201</v>
       </c>
       <c r="B3" t="n">
-        <v>104014</v>
+        <v>104015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36098-2023 artfynd.xlsx
+++ b/artfynd/A 36098-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137376201</v>
       </c>
       <c r="B3" t="n">
-        <v>104015</v>
+        <v>104018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36098-2023 artfynd.xlsx
+++ b/artfynd/A 36098-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137376200</v>
       </c>
       <c r="B2" t="n">
-        <v>61596</v>
+        <v>61600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137376201</v>
       </c>
       <c r="B3" t="n">
-        <v>104018</v>
+        <v>104023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
